--- a/www/download/COUNTRY.AUS.rpO2.xlsx
+++ b/www/download/COUNTRY.AUS.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Austrália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>1.34861762852899</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1.27722079147051</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1.34397767838582</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1.58881470938095</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>1.54959474777291</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1.71718034717616</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1.93184453411697</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1.83857323206392</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1.53402461090105</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1.35762575875635</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>1.30917466172452</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1.32740422194791</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1.19252052377757</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1.16922821167204</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1.26373683937823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.289</t>
+          <t>-0.877720067196736</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.355</t>
+          <t>-0.882528832693517</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.477</t>
+          <t>-0.846226306122498</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.642</t>
+          <t>-0.852617237299259</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.834</t>
+          <t>-0.906965611560031</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.012</t>
+          <t>-0.925943104048963</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>-0.916996697075144</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.367</t>
+          <t>-0.929046094179556</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.519</t>
+          <t>-0.929678426397921</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.774</t>
+          <t>-0.906126363038661</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.029</t>
+          <t>-0.939471381665022</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.288</t>
+          <t>-0.943259329994295</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.558</t>
+          <t>-0.945337393949613</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>10.861</t>
+          <t>-0.938373694189427</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>10.935</t>
+          <t>-0.915427989006947</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.001</t>
+          <t>-0.840157417229105</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.121</t>
+          <t>-0.845490934111972</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>-0.795997168652186</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.404</t>
+          <t>-0.802846287308245</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.566</t>
+          <t>-0.874714390752705</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.737</t>
+          <t>-0.899511211566184</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7.864</t>
+          <t>-0.886758694891155</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.082</t>
+          <t>-0.903612986223686</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>-0.904724165785576</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>-0.87039203438975</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>8.741</t>
+          <t>-0.91492490026702</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8.965</t>
+          <t>-0.920266997647104</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>9.202</t>
+          <t>-0.923228603288607</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>9.942</t>
+          <t>-0.913384402698037</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10.452</t>
+          <t>-0.881092769832915</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15262.516</t>
+          <t>-0.796835038052413</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15313.314</t>
+          <t>-0.804788083870844</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15492.621</t>
+          <t>-0.743974839592073</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15809.188</t>
+          <t>-0.754125597689546</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16175.072</t>
+          <t>-0.844608212931484</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16516.061</t>
+          <t>-0.87593147216485</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16578.653</t>
+          <t>-0.86095584293614</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16907.067</t>
+          <t>-0.882118412505374</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17174.77</t>
+          <t>-0.884043903569856</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17645.28</t>
+          <t>-0.842606301970499</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18026.47</t>
+          <t>-0.897008454320744</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18424.644</t>
+          <t>-0.903441239954049</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18919.606</t>
+          <t>-0.906989168107692</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20488.035</t>
+          <t>-0.895054129979023</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>21545.023</t>
+          <t>-0.855931028931936</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12828.687</t>
+          <t>349706482539.463</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12974.476</t>
+          <t>366446859982.686</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13053.68</t>
+          <t>289113401978.484</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13459.16</t>
+          <t>285568129633.589</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13759.368</t>
+          <t>472900715075.232</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14064.941</t>
+          <t>601041055516.363</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14063.118</t>
+          <t>592274796257.506</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14373.529</t>
+          <t>616611038329.906</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14680.712</t>
+          <t>717865772679.263</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15143.81</t>
+          <t>943021726224.442</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15580.662</t>
+          <t>1110435256340.09</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15917.851</t>
+          <t>1097810092728.64</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16341.758</t>
+          <t>1063313059567.15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17671.991</t>
+          <t>1019120350070.47</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>18590.196</t>
+          <t>804032085627.786</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>128728959487.377</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>134212763186.84</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>111334831392.766</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>116721962363.121</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>195438848367.3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>245388881404.374</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>251824732451.575</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>269489781627.388</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>309259455569.857</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>365740970171.243</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>424482809605.092</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>436761447563.401</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>409691185975.149</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>393918751393.925</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>302786126144.242</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>24345049.9967055</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>22816117.1229446</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>18628835.661079</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>20563005.4052722</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>32230360.3515103</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>42330297.5057876</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>45965371.3359364</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>41991425.7272939</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38429196.3568261</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39799487.713058</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>42283007.0698813</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>39244600.0083179</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>31482140.7719917</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>27952065.051838</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>21974208.2119378</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43.91</t>
+          <t>5243.40791191346</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>5282.49474263344</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>5535.45206761546</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>5366.52012549432</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>5161.41704725166</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>4030.50830991475</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>4359.39125049279</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>4228.06828113193</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>4831.38349100495</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>8321.26461059438</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>6063.359470127</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>6178.74938281843</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>7152.5372839947</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>8630.59013305473</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>10527.9517989542</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>146610.289414564</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>159526.213482853</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>123979.695883322</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>120450.347390909</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>185742.496535168</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>186186.938233551</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>174513.130482041</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>190918.985280122</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>227249.957496472</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>322455.394678893</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>367044.227854961</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>384562.520861652</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>474700.695051238</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>509090.748452466</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>463871.357345773</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>-0.831740976401443</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>-0.838601742473443</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>-0.788815481421025</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>-0.797689714997167</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>-0.87236617685789</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>-0.898484112822641</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>-0.886503719431654</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>-0.903968892131985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>-0.905574598747295</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>-0.872356665152105</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>-0.916896721847011</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>-0.922085416244953</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>-0.924892286891953</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>-0.91527873314475</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>-0.883762443704321</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>74031.509210943</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>79198.3107193253</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>85099.8371356917</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>75727.8216919794</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>81729.8547073177</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>81314.1176749028</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>73193.7582518738</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>76607.355863452</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>90572.4282288111</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>106576.139143213</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>117410.901612856</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>121206.247196359</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>139013.420886207</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>156046.444909782</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>153811.901354841</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.34861762852899</t>
+          <t>18387.7105004742</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.27722079147051</t>
+          <t>18847.9894375407</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.34397767838582</t>
+          <t>15465.2437990322</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.58881470938095</t>
+          <t>15764.1311759923</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.54959474777291</t>
+          <t>25831.3522043548</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.71718034717616</t>
+          <t>31717.0578470529</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93184453411697</t>
+          <t>32021.9851747779</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.83857323206392</t>
+          <t>33343.3286228111</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.53402461090105</t>
+          <t>37478.7050745343</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.35762575875635</t>
+          <t>43129.1564778512</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.30917466172452</t>
+          <t>48562.6145880894</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.32740422194791</t>
+          <t>48718.6744372829</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.19252052377757</t>
+          <t>44520.8565321283</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.16922821167204</t>
+          <t>39621.3498592078</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.26373683937823</t>
+          <t>28969.7656016955</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>288884269842.267</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>309679550896.387</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>242003277481.96</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>238709492838.832</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>438332914596.192</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>610838550871.333</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>622327430246.026</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>613426489829.239</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>688336416033.156</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>817647623230.988</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>990041504760.749</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>979720688823.948</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>908150420421.21</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>934218788157.003</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>697914005018.618</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>297286111446.926</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>315697351880.143</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>251686761226.92</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>246091736997.355</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>441479572376.198</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>606872486813.411</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>619837088500.938</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>610024496370.025</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>675126842127.718</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>806414164191.536</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>975121262864.289</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>968547823082.592</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>906086191879.199</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>921194303011.384</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>690531007092.57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>-8401841604.65892</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-6017800983.75569</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-9683483744.95987</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>-7382244158.52359</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>-3146657780.00586</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>3966064057.92175</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>2490341745.08786</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>3401993459.21464</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>13209573905.4381</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>11233459039.4515</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>14920241896.4595</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.907</t>
+          <t>11172865741.3565</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>2064228542.01042</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>13024485145.619</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>7382997926.04846</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>3093.89821502273</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>3042.03265309804</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>3266.02006640509</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>3189.24587103705</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>3296.95423877217</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>3219.78526599921</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>3634.37621375203</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>3201.99678765584</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>3538.94176509471</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>5505.14936200963</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>4035.71246795038</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>3795.89523987853</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.821</t>
+          <t>3343.8597197396</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>3356.77095458718</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>3367.3747599997</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>3043.70997389386</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>2993.96823670583</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>3208.93596734021</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>3136.82988398414</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>3239.2158117413</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>3168.94900627568</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>3590.83761768237</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>3175.50443024726</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>3510.35768295466</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>5448.4602290208</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>3984.2005002937</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>3750.64003443305</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>3313.89952255748</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>3497.4390476173</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>3662.30296615623</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-87.77</t>
+          <t>73925.3026335695</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>83143.7064783355</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-84.62</t>
+          <t>85657.6703586451</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>71546.4198589818</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-90.7</t>
+          <t>82657.7304240136</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-92.59</t>
+          <t>90273.7457606642</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-91.7</t>
+          <t>80344.7016223961</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-92.9</t>
+          <t>82430.8733489279</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-92.97</t>
+          <t>95572.9106667517</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-90.61</t>
+          <t>122754.293079389</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-93.95</t>
+          <t>149343.211598088</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-94.33</t>
+          <t>161914.494992754</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-94.53</t>
+          <t>195359.198755723</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-93.84</t>
+          <t>243242.166032765</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-91.54</t>
+          <t>200696.483372384</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-84.02</t>
+          <t>64714347061.7117</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-84.55</t>
+          <t>70540588405.8718</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-79.6</t>
+          <t>59137951076.5598</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-80.28</t>
+          <t>53291888795.9764</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-87.47</t>
+          <t>94839402190.2923</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-89.95</t>
+          <t>143099571078.953</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-88.68</t>
+          <t>136327103298.633</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>128453005776.877</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-90.47</t>
+          <t>143414736594.025</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-87.04</t>
+          <t>191745670526.301</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-91.49</t>
+          <t>250639670043.029</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-92.03</t>
+          <t>265492149172.958</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>269487552459.736</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-91.34</t>
+          <t>289694374088.833</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-88.11</t>
+          <t>180785066324.659</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-79.68</t>
+          <t>70489.1347399083</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-80.48</t>
+          <t>76231.1768153268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-74.4</t>
+          <t>82714.6367266814</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-75.41</t>
+          <t>74824.5762535685</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-84.46</t>
+          <t>85369.6177766899</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-87.59</t>
+          <t>83571.7943769528</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-86.1</t>
+          <t>75165.02782931</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-88.21</t>
+          <t>85725.6938519204</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-88.4</t>
+          <t>103238.447633734</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-84.26</t>
+          <t>131595.583649302</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-89.7</t>
+          <t>151441.704391143</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-90.34</t>
+          <t>161775.145211455</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-90.7</t>
+          <t>203614.145602268</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-89.51</t>
+          <t>223979.504872329</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-85.59</t>
+          <t>192821.087558172</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25228.764</t>
+          <t>339370743581.948</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25013.257</t>
+          <t>352772001288.36</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27202.07</t>
+          <t>291033850116.061</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27107.276</t>
+          <t>304309763074.876</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28613.742</t>
+          <t>546537358374.401</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28559.083</t>
+          <t>706836092879.768</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>32782.77</t>
+          <t>719638474945.558</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>29744.641</t>
+          <t>765657445414.229</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>33414.499</t>
+          <t>884845691005.866</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>53251.863</t>
+          <t>1065542572058.97</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>39957.052</t>
+          <t>1254671036809.17</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>38587.039</t>
+          <t>1244349057128.17</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>34989.484</t>
+          <t>1215723016091.72</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>37986.429</t>
+          <t>1146242524759.19</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40048.824</t>
+          <t>853167748680.843</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21659.809</t>
+          <t>3436.16789366122</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21661.706</t>
+          <t>6912.52966300878</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>23512.193</t>
+          <t>2943.03363196362</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>23614.053</t>
+          <t>-3278.15639458673</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>24944.607</t>
+          <t>-2711.88735267633</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24910.87</t>
+          <t>6701.95138371143</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>28581.17</t>
+          <t>5179.67379308611</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25879.402</t>
+          <t>-3294.82050299244</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29201.948</t>
+          <t>-7665.53696698253</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46684.397</t>
+          <t>-8841.29056991314</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>35275.913</t>
+          <t>-2098.49279305482</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>34030.086</t>
+          <t>139.349781299291</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>30770.968</t>
+          <t>-8254.9468465452</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>33373.296</t>
+          <t>19262.6611604358</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>35195.119</t>
+          <t>7875.39581421205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>349706.483</t>
+          <t>-274656396520.236</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>366446.86</t>
+          <t>-282231412882.488</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>289113.402</t>
+          <t>-231895899039.501</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>285568.13</t>
+          <t>-251017874278.9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>472900.715</t>
+          <t>-451697956184.109</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>601041.056</t>
+          <t>-563736521800.815</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>592274.796</t>
+          <t>-583311371646.925</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>616611.038</t>
+          <t>-637204439637.352</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>717865.773</t>
+          <t>-741430954411.842</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>943021.726</t>
+          <t>-873796901532.667</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1110435.256</t>
+          <t>-1004031366766.14</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1097810.093</t>
+          <t>-978856907955.208</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1063313.06</t>
+          <t>-946235463631.98</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1019120.35</t>
+          <t>-856548150670.353</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>804032.086</t>
+          <t>-672382682356.184</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>163327.24381</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>178191.58657</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>177514.85328</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>156770.95752</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>169037.74314</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>161160.70924</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>153651.59963</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>169217.48267</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>218098.91304</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>268298.36943</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>308739.17335</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>326150.75571</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>387434.68136</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>426399.06147</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>431019.08545</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12506.992</t>
+          <t>0.0370328827118346</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12134.392</t>
+          <t>0.0412947930615338</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12908.351</t>
+          <t>0.0428288174215696</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12723.144</t>
+          <t>0.0444688691063616</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13140.977</t>
+          <t>0.0484719947053628</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>13011.122</t>
+          <t>0.0456376454920952</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14795.205</t>
+          <t>0.055740460686857</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13655.392</t>
+          <t>0.062690482003955</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>15261.982</t>
+          <t>0.0745508024174448</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>24335.562</t>
+          <t>0.0785655204106469</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18343.752</t>
+          <t>0.0846975534192888</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>17638.467</t>
+          <t>0.0878669519602035</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>16021.435</t>
+          <t>0.0965892638355247</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>17277.097</t>
+          <t>0.0970063354437479</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>18248.187</t>
+          <t>0.100361075594903</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>189868.494299314</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>213941.082808452</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>211949.947596942</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>190483.508639969</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>205915.128769095</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>197591.943818719</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>184329.016168008</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>204239.350027981</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>260832.844519709</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>317552.901824903</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>354812.091731048</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>383147.040357706</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>462040.19248977</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>511098.123781348</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>498689.56142909</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>128728.959</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>134212.763</t>
+          <t>247042.561166084</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>111334.831</t>
+          <t>245212.233573625</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>116721.962</t>
+          <t>218661.70000032</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>195438.848</t>
+          <t>236203.455246225</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>245388.881</t>
+          <t>226529.411581485</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>251824.732</t>
+          <t>211426.463917418</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>269489.782</t>
+          <t>234743.684481662</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>309259.456</t>
+          <t>298459.503014282</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>365740.97</t>
+          <t>362225.598050155</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>424482.81</t>
+          <t>401895.913603307</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>436761.448</t>
+          <t>434454.075255592</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>409691.186</t>
+          <t>525383.13595245</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>393918.751</t>
+          <t>581746.34502725</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>302786.126</t>
+          <t>567463.067505893</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-83.17</t>
+          <t>1538087.02899907</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>1590164.74926371</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-78.88</t>
+          <t>1500355.89328043</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-79.77</t>
+          <t>1283312.26438895</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-87.24</t>
+          <t>1330856.39715423</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>1269664.39282344</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-88.65</t>
+          <t>1132604.27923937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-90.4</t>
+          <t>1202551.23465361</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-90.56</t>
+          <t>1469065.97468466</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-87.24</t>
+          <t>1726600.80144075</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-91.69</t>
+          <t>1855848.27386571</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>1907051.14573615</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-92.49</t>
+          <t>2169376.54425187</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>2388624.46234074</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-88.38</t>
+          <t>2294004.94937459</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>24.345</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22.816</t>
+          <t>230599.404506205</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18.629</t>
+          <t>237949.153674314</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20.563</t>
+          <t>250262.060632838</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>258406.949753336</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>266933.464059074</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>45.965</t>
+          <t>271889.799504023</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>41.991</t>
+          <t>278369.726039547</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>38.429</t>
+          <t>283092.560448583</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>39.799</t>
+          <t>293634.41830284</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>42.283</t>
+          <t>304609.966543906</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>39.245</t>
+          <t>316215.071145613</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>31.482</t>
+          <t>330465.34834293</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>27.952</t>
+          <t>343645.299165299</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>21.974</t>
+          <t>349635.715183621</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>189868.494299314</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>199357.59835537</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>204863.833201284</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>217116.193006002</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>224556.335046558</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>232338.016803165</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>236773.447442399</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>241378.895999344</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>246305.587297869</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>256072.998226462</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>266920.936391972</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>276821.926296917</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>288651.609567658</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>299855.339807324</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>304287.653401073</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>130991.30575646</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>144863.834973916</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>149358.305756375</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>132795.26679968</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>146239.118943776</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>139258.611128515</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>136325.642552582</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>151995.872398338</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>200092.475445718</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>242227.429649845</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>274596.709926693</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>288773.018604408</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>348551.90427755</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>387758.15075275</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>384040.705494107</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21659809032.2043</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21661706116.1805</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>23512192768.7526</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>23614053471.7728</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>24944607407.6095</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>24910869999.2249</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>28581170488.3728</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>25879402288.7874</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>29201948183.3771</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>46684397123.162</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>35275912997.7741</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>34030086387.1539</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>30770968059.1169</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>33373295656.1317</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>35195119383.2418</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>25228764105.8109</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>25013257331.9707</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>27202069971.7438</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>27107276177.8856</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>28613742441.6492</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>28559082996.2405</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>32782770377.6695</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>29744641493.5262</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>33414499458.104</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>53251863139.5549</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>39957052233.6587</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>38587038799.5065</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>34989483508.0813</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>37986429349.0818</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>40048823859.9123</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>12506992140.2985</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>12134392016.5268</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12908350575.9141</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>12723144001.4434</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>13140976663.8119</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>13011122003.7352</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>14795205137.6333</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13655391940.8975</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>15261982361.1362</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>24335562210.9141</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18343751560.5153</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>17638467258.0695</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>16021434942.8993</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>17277096597.1201</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>18248186503.1219</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8288820</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8354550</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>8476975</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8641615</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8833540</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9012162.372977</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9129560.80671462</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9366902.84863187</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9518830.40875171</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9773745.40717266</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10028875.8637305</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10288121.0794038</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10558402.0486772</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10861212.6850247</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10935420.7530093</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7000815</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7120800</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7199035</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7404275</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7565955</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7736810.98</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7864119.95</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8082269.91</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8251604.61</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8480132.7</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8740938.13122661</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>8964969.8520771</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>9202230.54737272</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>9942083.06364353</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>10451797.5846695</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15262515700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>15313313900</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>15492620800</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15809187500</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>16175072100</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16516060800</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16578652800</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16907066600</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17174769880</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17645279900</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>18026470142.4781</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>18424644486.6276</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>18919606150.8565</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>20488034752.5043</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>21545022822.5012</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>12828686900</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>12974476100</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13053680400</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13459159500</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>13759368400</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14064941400</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14063117500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14373529200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14680711620</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15143809500</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>15580661526.7842</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>15917851279.2693</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16341757580.232</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>17671991252.385</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>18590195705.1333</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153864968584301</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16029700854778</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.166954385727705</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.173855008300376</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.181019712145316</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.188472308501638</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.196239816083751</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.204603232753246</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.210571051646447</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.209717359901643</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.37847368190924</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.378806594382501</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.379326311097916</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.380031673104945</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.380924411145202</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.382009092927736</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.383293158770534</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.381499114359128</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.380542432698167</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.392477390240563</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.439089920935031</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.43232496849829</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.425147874602951</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.41754189002325</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.409484448138053</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.400947169999198</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.391895596574286</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.385326224316197</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.380315087083958</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.369233821286366</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.10955143095146</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.114780512886299</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.120147617578139</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.12567559535655</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.131389805509691</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.137318730790312</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.143494728361388</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.148230307978723</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.151492247330357</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.148429770757862</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.348362937765847</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.350930694736798</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.353661187586671</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.356573334821328</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.359688922457053</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.363033185664254</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.366635535000485</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.365531045509784</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.364773902744126</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.37936587381734</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.513514202711263</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.505717363805475</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.497619766263762</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.489179641250694</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.480349843461828</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.471076654974004</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.461298308066698</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.457667217940064</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.455162421354089</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.443632926853369</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>752494.98168</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>829399.27125</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>832678.26478</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>752129.87266</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>815120.20972</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>781105.49249</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>735918.42278</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>818548.85189</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1043916.75928</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1274561.85401</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1413363.26662</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1511399.28909</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1821221.24465</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2017526.35779</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1968895.58857</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>352145.03092</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>391906.39614</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>394570.53933</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>351456.9668</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>382442.57419</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>365788.02271</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>347752.10647</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>386739.55688</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>498551.97846</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>604453.0277</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>676492.62353</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>723227.09386</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>873935.04023</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>969504.49578</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>951503.773</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2074291.31844027</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2058486.2850259</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2058015.25273273</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2067393.1610367</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2094191.92939219</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2109019.69877836</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2139196.35186379</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2199026.60809042</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2286993.16578155</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2403523.49034269</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2553520.13918935</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2731277.7005298</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2980149.29532968</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3230346.10392524</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3478011.97184729</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
